--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-02-2026.xlsx
@@ -2172,7 +2172,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-pl4025-high-performance-board-insulation-2400-x-1200-x-37-5mm</t>
+          <t>£32.87</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>£35.65</t>
+          <t>£34.78</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/62-5mm-celotex-pl4050-pir-insulated-plasterboard-2400mm-x-1200mm</t>
+          <t>£43.29</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /50mm-celotex-cw4050-50mm-cavity-insulation-1200-x-450mm---11-boards-per-pack-726-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x00000134B5014690&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
+          <t>£47.47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
